--- a/sheets/민요/검수/노래가락 (청성).xlsx
+++ b/sheets/민요/검수/노래가락 (청성).xlsx
@@ -4,14 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -20,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -50,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -73,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +176,54 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4591,8 +4719,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:O18"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -4609,996 +4741,877 @@
     <col min="15" max="15" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">노래가락 — 민요채보-3/노래가락.png</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">노래가락</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+      <c s="8" r="L2"/>
+      <c s="8" r="M2"/>
+      <c s="8" r="N2"/>
+      <c s="8" r="O2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="H3" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="J3" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="L3" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">호</t>
         </is>
       </c>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="N3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">一△</t>
         </is>
       </c>
-      <c r="O3" s="5" t="inlineStr">
+      <c r="O3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">바</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">一</t>
-        </is>
-      </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">一</t>
-        </is>
-      </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="C4" s="19"/>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">一</t>
+        </is>
+      </c>
+      <c r="E4" s="20"/>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">一</t>
+        </is>
+      </c>
+      <c r="G4" s="20"/>
+      <c r="H4" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="J4" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K4" s="19"/>
+      <c r="L4" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M4" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O4" s="2"/>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">一</t>
-        </is>
-      </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">一</t>
-        </is>
-      </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="N4" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O4" s="19"/>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">一</t>
+        </is>
+      </c>
+      <c r="C5" s="20"/>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">一</t>
+        </is>
+      </c>
+      <c r="E5" s="20"/>
+      <c r="F5" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">一仲</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="H5" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I5" s="19"/>
+      <c r="J5" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K5" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="L5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢無</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="M5" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="N5" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O5" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">람</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C6" s="21"/>
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="E6" s="21"/>
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">一</t>
-        </is>
-      </c>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">一</t>
-        </is>
-      </c>
-      <c r="K6" s="5"/>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M6" s="2"/>
-      <c r="N6" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">一</t>
-        </is>
-      </c>
-      <c r="O6" s="5"/>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="G6" s="21"/>
+      <c r="H6" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">一</t>
+        </is>
+      </c>
+      <c r="I6" s="22"/>
+      <c r="J6" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">一</t>
+        </is>
+      </c>
+      <c r="K6" s="22"/>
+      <c r="L6" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M6" s="21"/>
+      <c r="N6" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">一</t>
+        </is>
+      </c>
+      <c r="O6" s="22"/>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">潢仲</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">一潢潢</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="J7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">一仲</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="K7" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="L7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="M7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="N7" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">세</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">潢仲</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">潢仲</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">潢仲潢</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="H8" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I8" s="19"/>
+      <c r="J8" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K8" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="L8" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">姑仲</t>
         </is>
       </c>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O8" s="2"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">一</t>
-        </is>
-      </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">一</t>
-        </is>
-      </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">一</t>
-        </is>
-      </c>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">一</t>
-        </is>
-      </c>
-      <c r="I9" s="5"/>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="M8" s="19"/>
+      <c r="N8" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O8" s="19"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">一</t>
+        </is>
+      </c>
+      <c r="C9" s="20"/>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">一</t>
+        </is>
+      </c>
+      <c r="E9" s="20"/>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">一</t>
+        </is>
+      </c>
+      <c r="G9" s="20"/>
+      <c r="H9" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">一</t>
+        </is>
+      </c>
+      <c r="I9" s="20"/>
+      <c r="J9" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K9" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L9" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M9" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
-      <c r="N9" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">一</t>
-        </is>
-      </c>
-      <c r="O9" s="5"/>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="N9" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">一</t>
+        </is>
+      </c>
+      <c r="O9" s="20"/>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C10" s="21"/>
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="E10" s="21"/>
+      <c r="F10" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G10" s="21"/>
+      <c r="H10" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="I10" s="21"/>
+      <c r="J10" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K10" s="2"/>
-      <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">一</t>
-        </is>
-      </c>
-      <c r="M10" s="5"/>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O10" s="2"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">一</t>
-        </is>
-      </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K10" s="21"/>
+      <c r="L10" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">一</t>
+        </is>
+      </c>
+      <c r="M10" s="22"/>
+      <c r="N10" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O10" s="21"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">一</t>
+        </is>
+      </c>
+      <c r="C11" s="18"/>
+      <c r="D11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="E11" s="17"/>
+      <c r="F11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">날</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">제</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="L11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="M11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">더</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O11" s="2"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="N11" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O11" s="17"/>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C12" s="19"/>
+      <c r="D12" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="E12" s="19"/>
+      <c r="F12" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G12" s="19"/>
+      <c r="H12" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="I12" s="19"/>
+      <c r="J12" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="K12" s="19"/>
+      <c r="L12" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="M12" s="2"/>
-      <c r="N12" s="5" t="inlineStr">
+      <c r="M12" s="19"/>
+      <c r="N12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">一仲</t>
         </is>
       </c>
-      <c r="O12" s="5"/>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="O12" s="20"/>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C13" s="19"/>
+      <c r="D13" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="E13" s="19"/>
+      <c r="F13" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢無南</t>
         </is>
       </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G13" s="19"/>
+      <c r="H13" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢無</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I13" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J13" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">潢仲</t>
         </is>
       </c>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="K13" s="19"/>
+      <c r="L13" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="M13" s="19"/>
+      <c r="N13" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="O13" s="2"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="O13" s="19"/>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C14" s="21"/>
+      <c r="D14" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="E14" s="21"/>
+      <c r="F14" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G14" s="21"/>
+      <c r="H14" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="I14" s="21"/>
+      <c r="J14" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="K14" s="21"/>
+      <c r="L14" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢潢</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="M14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O14" s="2"/>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="1">
-        <v>13</v>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="N14" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O14" s="21"/>
+    </row>
+    <row r="15" ht="56" customHeight="1">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢無</t>
         </is>
       </c>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="E15" s="17"/>
+      <c r="F15" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G15" s="17"/>
+      <c r="H15" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="I15" s="17"/>
+      <c r="J15" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢潢潢</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="K15" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="L15" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="M15" s="17"/>
+      <c r="N15" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O15" s="2"/>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="1">
-        <v>14</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="O15" s="17"/>
+    </row>
+    <row r="16" ht="56" customHeight="1">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C16" s="19"/>
+      <c r="D16" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="E16" s="19"/>
+      <c r="F16" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G16" s="19"/>
+      <c r="H16" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I16" s="19"/>
+      <c r="J16" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O16" s="2"/>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="1">
-        <v>15</v>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="K16" s="19"/>
+      <c r="L16" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M16" s="19"/>
+      <c r="N16" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O16" s="19"/>
+    </row>
+    <row r="17" ht="56" customHeight="1">
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C17" s="19"/>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E17" s="19"/>
+      <c r="F17" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G17" s="19"/>
+      <c r="H17" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="I17" s="19"/>
+      <c r="J17" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K17" s="19"/>
+      <c r="L17" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="M17" s="2"/>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="M17" s="19"/>
+      <c r="N17" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="O17" s="2"/>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="1">
-        <v>16</v>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">一</t>
-        </is>
-      </c>
-      <c r="C18" s="5"/>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="O17" s="19"/>
+    </row>
+    <row r="18" ht="56" customHeight="1">
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">一</t>
+        </is>
+      </c>
+      <c r="C18" s="22"/>
+      <c r="D18" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I18" s="2"/>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">一</t>
-        </is>
-      </c>
-      <c r="K18" s="5"/>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="E18" s="21"/>
+      <c r="F18" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G18" s="21"/>
+      <c r="H18" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I18" s="21"/>
+      <c r="J18" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">一</t>
+        </is>
+      </c>
+      <c r="K18" s="22"/>
+      <c r="L18" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
       </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O18" s="2"/>
+      <c r="N18" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O18" s="21"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:O2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="77"/>
 </worksheet>
 </file>